--- a/Result/profitability/6203.xlsx
+++ b/Result/profitability/6203.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09875</v>
+        <v>1.19375</v>
       </c>
       <c r="N2" t="n">
-        <v>31.43875</v>
+        <v>32.6575</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.26</v>
       </c>
       <c r="M3" t="n">
-        <v>1.28625</v>
+        <v>1.23875</v>
       </c>
       <c r="N3" t="n">
-        <v>32.45875</v>
+        <v>32.58125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>1.98</v>
       </c>
       <c r="M4" t="n">
-        <v>1.42125</v>
+        <v>1.2575</v>
       </c>
       <c r="N4" t="n">
-        <v>32.61125</v>
+        <v>32.07125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.45</v>
       </c>
       <c r="M5" t="n">
-        <v>1.37375</v>
+        <v>1.56375</v>
       </c>
       <c r="N5" t="n">
-        <v>32.34375</v>
+        <v>31.5225</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,13 +1137,13 @@
         <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>1.67875</v>
+        <v>1.4375</v>
       </c>
       <c r="N6" t="n">
-        <v>32.2875</v>
+        <v>31.43875</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1152,10 +1152,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.69</v>
       </c>
       <c r="M7" t="n">
-        <v>1.58375</v>
+        <v>1.37</v>
       </c>
       <c r="N7" t="n">
-        <v>32.0025</v>
+        <v>31.36125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>1.47125</v>
+        <v>1.365</v>
       </c>
       <c r="N8" t="n">
-        <v>31.96625</v>
+        <v>31.68</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>470</v>
+      </c>
+      <c r="D75" t="n">
+        <v>334</v>
+      </c>
+      <c r="E75" t="n">
+        <v>136</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="G75" t="n">
+        <v>37</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.85%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>33</v>
+      </c>
+      <c r="J75" t="n">
+        <v>70</v>
+      </c>
+      <c r="K75" t="n">
+        <v>43</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.80625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.8500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6204379562043796</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.289999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07316293929712459</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.569999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1846543001686339</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
